--- a/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/DTO/ItemsDTO_クラス仕様書.xlsx
+++ b/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/DTO/ItemsDTO_クラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C8081A-0190-4613-8A06-04A5599A5720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A3D75C-0B1B-4135-9C02-BCDE300F6019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="メソッド仕様（）(引数有り)" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（）'!$A$1:$BI$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'メソッド仕様（）(引数有り)'!$A$1:$BI$19</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -339,6 +339,10 @@
       <t>ヘンスウ</t>
     </rPh>
     <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>manufacture</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -911,23 +915,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -944,47 +978,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1004,19 +1020,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1362,90 +1366,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IX24"/>
+  <dimension ref="A1:IX25"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="37" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="38" t="s">
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="37" t="s">
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
-      <c r="AP1" s="38"/>
-      <c r="AQ1" s="37" t="s">
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="38" t="s">
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="38"/>
-      <c r="AX1" s="38"/>
-      <c r="AY1" s="38"/>
-      <c r="AZ1" s="38"/>
-      <c r="BA1" s="37" t="s">
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="42">
+      <c r="BB1" s="51"/>
+      <c r="BC1" s="51"/>
+      <c r="BD1" s="52">
         <v>45555</v>
       </c>
-      <c r="BE1" s="42"/>
-      <c r="BF1" s="42"/>
-      <c r="BG1" s="42"/>
-      <c r="BH1" s="42"/>
-      <c r="BI1" s="42"/>
+      <c r="BE1" s="52"/>
+      <c r="BF1" s="52"/>
+      <c r="BG1" s="52"/>
+      <c r="BH1" s="52"/>
+      <c r="BI1" s="52"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1645,77 +1649,77 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="37" t="s">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="37" t="s">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="38" t="s">
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="37" t="s">
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="37"/>
-      <c r="AS2" s="37"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="38"/>
-      <c r="AX2" s="38"/>
-      <c r="AY2" s="38"/>
-      <c r="AZ2" s="38"/>
-      <c r="BA2" s="37" t="s">
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="37"/>
-      <c r="BC2" s="37"/>
-      <c r="BD2" s="42"/>
-      <c r="BE2" s="42"/>
-      <c r="BF2" s="42"/>
-      <c r="BG2" s="42"/>
-      <c r="BH2" s="42"/>
-      <c r="BI2" s="42"/>
+      <c r="BB2" s="51"/>
+      <c r="BC2" s="51"/>
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1915,239 +1919,239 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="49" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50"/>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="50"/>
-      <c r="AD4" s="50"/>
-      <c r="AE4" s="50"/>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="50"/>
-      <c r="AH4" s="50"/>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="50"/>
-      <c r="AL4" s="50"/>
-      <c r="AM4" s="50"/>
-      <c r="AN4" s="50"/>
-      <c r="AO4" s="50"/>
-      <c r="AP4" s="50"/>
-      <c r="AQ4" s="50"/>
-      <c r="AR4" s="50"/>
-      <c r="AS4" s="50"/>
-      <c r="AT4" s="50"/>
-      <c r="AU4" s="50"/>
-      <c r="AV4" s="50"/>
-      <c r="AW4" s="50"/>
-      <c r="AX4" s="50"/>
-      <c r="AY4" s="50"/>
-      <c r="AZ4" s="50"/>
-      <c r="BA4" s="50"/>
-      <c r="BB4" s="50"/>
-      <c r="BC4" s="50"/>
-      <c r="BD4" s="50"/>
-      <c r="BE4" s="50"/>
-      <c r="BF4" s="50"/>
-      <c r="BG4" s="50"/>
-      <c r="BH4" s="50"/>
-      <c r="BI4" s="51"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="43"/>
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="43"/>
+      <c r="AD4" s="43"/>
+      <c r="AE4" s="43"/>
+      <c r="AF4" s="43"/>
+      <c r="AG4" s="43"/>
+      <c r="AH4" s="43"/>
+      <c r="AI4" s="43"/>
+      <c r="AJ4" s="43"/>
+      <c r="AK4" s="43"/>
+      <c r="AL4" s="43"/>
+      <c r="AM4" s="43"/>
+      <c r="AN4" s="43"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AQ4" s="43"/>
+      <c r="AR4" s="43"/>
+      <c r="AS4" s="43"/>
+      <c r="AT4" s="43"/>
+      <c r="AU4" s="43"/>
+      <c r="AV4" s="43"/>
+      <c r="AW4" s="43"/>
+      <c r="AX4" s="43"/>
+      <c r="AY4" s="43"/>
+      <c r="AZ4" s="43"/>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43"/>
+      <c r="BC4" s="43"/>
+      <c r="BD4" s="43"/>
+      <c r="BE4" s="43"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
+      <c r="BI4" s="44"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="49" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="50"/>
-      <c r="AD5" s="50"/>
-      <c r="AE5" s="50"/>
-      <c r="AF5" s="50"/>
-      <c r="AG5" s="50"/>
-      <c r="AH5" s="50"/>
-      <c r="AI5" s="50"/>
-      <c r="AJ5" s="50"/>
-      <c r="AK5" s="50"/>
-      <c r="AL5" s="50"/>
-      <c r="AM5" s="50"/>
-      <c r="AN5" s="50"/>
-      <c r="AO5" s="50"/>
-      <c r="AP5" s="50"/>
-      <c r="AQ5" s="50"/>
-      <c r="AR5" s="50"/>
-      <c r="AS5" s="50"/>
-      <c r="AT5" s="50"/>
-      <c r="AU5" s="50"/>
-      <c r="AV5" s="50"/>
-      <c r="AW5" s="50"/>
-      <c r="AX5" s="50"/>
-      <c r="AY5" s="50"/>
-      <c r="AZ5" s="50"/>
-      <c r="BA5" s="50"/>
-      <c r="BB5" s="50"/>
-      <c r="BC5" s="50"/>
-      <c r="BD5" s="50"/>
-      <c r="BE5" s="50"/>
-      <c r="BF5" s="50"/>
-      <c r="BG5" s="50"/>
-      <c r="BH5" s="50"/>
-      <c r="BI5" s="51"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="43"/>
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="43"/>
+      <c r="AD5" s="43"/>
+      <c r="AE5" s="43"/>
+      <c r="AF5" s="43"/>
+      <c r="AG5" s="43"/>
+      <c r="AH5" s="43"/>
+      <c r="AI5" s="43"/>
+      <c r="AJ5" s="43"/>
+      <c r="AK5" s="43"/>
+      <c r="AL5" s="43"/>
+      <c r="AM5" s="43"/>
+      <c r="AN5" s="43"/>
+      <c r="AO5" s="43"/>
+      <c r="AP5" s="43"/>
+      <c r="AQ5" s="43"/>
+      <c r="AR5" s="43"/>
+      <c r="AS5" s="43"/>
+      <c r="AT5" s="43"/>
+      <c r="AU5" s="43"/>
+      <c r="AV5" s="43"/>
+      <c r="AW5" s="43"/>
+      <c r="AX5" s="43"/>
+      <c r="AY5" s="43"/>
+      <c r="AZ5" s="43"/>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43"/>
+      <c r="BC5" s="43"/>
+      <c r="BD5" s="43"/>
+      <c r="BE5" s="43"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
+      <c r="BI5" s="44"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="49" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="50"/>
-      <c r="Z6" s="50"/>
-      <c r="AA6" s="50"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="50"/>
-      <c r="AD6" s="50"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="47" t="s">
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="43"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="43"/>
+      <c r="AE6" s="44"/>
+      <c r="AF6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="AG6" s="47"/>
-      <c r="AH6" s="47"/>
-      <c r="AI6" s="47"/>
-      <c r="AJ6" s="47"/>
-      <c r="AK6" s="47"/>
-      <c r="AL6" s="48" t="s">
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="AM6" s="48"/>
-      <c r="AN6" s="48"/>
-      <c r="AO6" s="48"/>
-      <c r="AP6" s="48"/>
-      <c r="AQ6" s="48"/>
-      <c r="AR6" s="48"/>
-      <c r="AS6" s="48"/>
-      <c r="AT6" s="48"/>
-      <c r="AU6" s="48"/>
-      <c r="AV6" s="48"/>
-      <c r="AW6" s="48"/>
-      <c r="AX6" s="48"/>
-      <c r="AY6" s="48"/>
-      <c r="AZ6" s="48"/>
-      <c r="BA6" s="48"/>
-      <c r="BB6" s="48"/>
-      <c r="BC6" s="48"/>
-      <c r="BD6" s="48"/>
-      <c r="BE6" s="48"/>
-      <c r="BF6" s="48"/>
-      <c r="BG6" s="48"/>
-      <c r="BH6" s="48"/>
-      <c r="BI6" s="48"/>
+      <c r="AM6" s="57"/>
+      <c r="AN6" s="57"/>
+      <c r="AO6" s="57"/>
+      <c r="AP6" s="57"/>
+      <c r="AQ6" s="57"/>
+      <c r="AR6" s="57"/>
+      <c r="AS6" s="57"/>
+      <c r="AT6" s="57"/>
+      <c r="AU6" s="57"/>
+      <c r="AV6" s="57"/>
+      <c r="AW6" s="57"/>
+      <c r="AX6" s="57"/>
+      <c r="AY6" s="57"/>
+      <c r="AZ6" s="57"/>
+      <c r="BA6" s="57"/>
+      <c r="BB6" s="57"/>
+      <c r="BC6" s="57"/>
+      <c r="BD6" s="57"/>
+      <c r="BE6" s="57"/>
+      <c r="BF6" s="57"/>
+      <c r="BG6" s="57"/>
+      <c r="BH6" s="57"/>
+      <c r="BI6" s="57"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="45"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="55"/>
       <c r="Y8" s="10"/>
       <c r="Z8" s="10"/>
       <c r="AA8" s="10"/>
@@ -2187,34 +2191,34 @@
       <c r="BI8" s="10"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40" t="s">
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="41"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="61"/>
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
       <c r="AA9" s="10"/>
@@ -2254,34 +2258,34 @@
       <c r="BI9" s="10"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40" t="s">
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="41"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="61"/>
       <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="10"/>
@@ -2321,34 +2325,34 @@
       <c r="BI10" s="10"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="70" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="R11" s="68"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="68"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="68"/>
-      <c r="W11" s="68"/>
-      <c r="X11" s="71"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="49"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
       <c r="AA11" s="10"/>
@@ -2388,34 +2392,34 @@
       <c r="BI11" s="10"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67" t="s">
-        <v>32</v>
+      <c r="A12" s="45" t="s">
+        <v>61</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="68"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="70" t="s">
-        <v>36</v>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="48" t="s">
+        <v>37</v>
       </c>
-      <c r="R12" s="68"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="68"/>
-      <c r="U12" s="68"/>
-      <c r="V12" s="68"/>
-      <c r="W12" s="68"/>
-      <c r="X12" s="71"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="49"/>
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="10"/>
@@ -2455,34 +2459,34 @@
       <c r="BI12" s="10"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="67" t="s">
-        <v>33</v>
+      <c r="A13" s="45" t="s">
+        <v>32</v>
       </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="70" t="s">
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="R13" s="68"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="68"/>
-      <c r="V13" s="68"/>
-      <c r="W13" s="68"/>
-      <c r="X13" s="71"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="49"/>
       <c r="Y13" s="10"/>
       <c r="Z13" s="10"/>
       <c r="AA13" s="10"/>
@@ -2522,34 +2526,34 @@
       <c r="BI13" s="10"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="67" t="s">
-        <v>34</v>
+      <c r="A14" s="45" t="s">
+        <v>33</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="70" t="s">
-        <v>38</v>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="48" t="s">
+        <v>36</v>
       </c>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="68"/>
-      <c r="W14" s="68"/>
-      <c r="X14" s="71"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="49"/>
       <c r="Y14" s="10"/>
       <c r="Z14" s="10"/>
       <c r="AA14" s="10"/>
@@ -2589,34 +2593,34 @@
       <c r="BI14" s="10"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54" t="s">
-        <v>35</v>
+      <c r="A15" s="45" t="s">
+        <v>34</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55" t="s">
-        <v>39</v>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="48" t="s">
+        <v>38</v>
       </c>
-      <c r="R15" s="55"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="55"/>
-      <c r="U15" s="55"/>
-      <c r="V15" s="55"/>
-      <c r="W15" s="55"/>
-      <c r="X15" s="56"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="49"/>
       <c r="Y15" s="10"/>
       <c r="Z15" s="10"/>
       <c r="AA15" s="10"/>
@@ -2656,6 +2660,34 @@
       <c r="BI15" s="10"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="41"/>
       <c r="Y16" s="10"/>
       <c r="Z16" s="10"/>
       <c r="AA16" s="10"/>
@@ -2694,472 +2726,499 @@
       <c r="BH16" s="10"/>
       <c r="BI16" s="10"/>
     </row>
-    <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47" t="s">
+    <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="10"/>
+      <c r="AJ17" s="10"/>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="10"/>
+      <c r="AN17" s="10"/>
+      <c r="AO17" s="10"/>
+      <c r="AP17" s="10"/>
+      <c r="AQ17" s="10"/>
+      <c r="AR17" s="10"/>
+      <c r="AS17" s="10"/>
+      <c r="AT17" s="10"/>
+      <c r="AU17" s="10"/>
+      <c r="AV17" s="10"/>
+      <c r="AW17" s="10"/>
+      <c r="AX17" s="10"/>
+      <c r="AY17" s="10"/>
+      <c r="AZ17" s="10"/>
+      <c r="BA17" s="10"/>
+      <c r="BB17" s="10"/>
+      <c r="BC17" s="10"/>
+      <c r="BD17" s="10"/>
+      <c r="BE17" s="10"/>
+      <c r="BF17" s="10"/>
+      <c r="BG17" s="10"/>
+      <c r="BH17" s="10"/>
+      <c r="BI17" s="10"/>
+    </row>
+    <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="47"/>
-      <c r="O18" s="47"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="47"/>
-      <c r="T18" s="47"/>
-      <c r="U18" s="47"/>
-      <c r="V18" s="47"/>
-      <c r="W18" s="47"/>
-      <c r="X18" s="47"/>
-      <c r="Y18" s="47"/>
-      <c r="Z18" s="47"/>
-      <c r="AA18" s="47"/>
-      <c r="AB18" s="47"/>
-      <c r="AC18" s="47"/>
-      <c r="AD18" s="47"/>
-      <c r="AE18" s="47"/>
-      <c r="AF18" s="47"/>
-      <c r="AG18" s="47"/>
-      <c r="AH18" s="47"/>
-      <c r="AI18" s="47"/>
-      <c r="AJ18" s="47"/>
-      <c r="AK18" s="47"/>
-      <c r="AL18" s="47"/>
-      <c r="AM18" s="47"/>
-      <c r="AN18" s="47"/>
-      <c r="AO18" s="47"/>
-      <c r="AP18" s="47"/>
-      <c r="AQ18" s="47"/>
-      <c r="AR18" s="47"/>
-      <c r="AS18" s="47"/>
-      <c r="AT18" s="47"/>
-      <c r="AU18" s="47"/>
-      <c r="AV18" s="47"/>
-      <c r="AW18" s="47"/>
-      <c r="AX18" s="47"/>
-      <c r="AY18" s="47"/>
-      <c r="AZ18" s="47"/>
-      <c r="BA18" s="47"/>
-      <c r="BB18" s="47"/>
-      <c r="BC18" s="47"/>
-      <c r="BD18" s="47"/>
-      <c r="BE18" s="47"/>
-      <c r="BF18" s="47"/>
-      <c r="BG18" s="47"/>
-      <c r="BH18" s="47"/>
-      <c r="BI18" s="47"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="38"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="38"/>
+      <c r="AJ19" s="38"/>
+      <c r="AK19" s="38"/>
+      <c r="AL19" s="38"/>
+      <c r="AM19" s="38"/>
+      <c r="AN19" s="38"/>
+      <c r="AO19" s="38"/>
+      <c r="AP19" s="38"/>
+      <c r="AQ19" s="38"/>
+      <c r="AR19" s="38"/>
+      <c r="AS19" s="38"/>
+      <c r="AT19" s="38"/>
+      <c r="AU19" s="38"/>
+      <c r="AV19" s="38"/>
+      <c r="AW19" s="38"/>
+      <c r="AX19" s="38"/>
+      <c r="AY19" s="38"/>
+      <c r="AZ19" s="38"/>
+      <c r="BA19" s="38"/>
+      <c r="BB19" s="38"/>
+      <c r="BC19" s="38"/>
+      <c r="BD19" s="38"/>
+      <c r="BE19" s="38"/>
+      <c r="BF19" s="38"/>
+      <c r="BG19" s="38"/>
+      <c r="BH19" s="38"/>
+      <c r="BI19" s="38"/>
     </row>
-    <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="52" t="s">
+    <row r="20" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="53"/>
-      <c r="U19" s="53"/>
-      <c r="V19" s="53"/>
-      <c r="W19" s="53"/>
-      <c r="X19" s="53"/>
-      <c r="Y19" s="53"/>
-      <c r="Z19" s="53"/>
-      <c r="AA19" s="53"/>
-      <c r="AB19" s="53"/>
-      <c r="AC19" s="53"/>
-      <c r="AD19" s="53"/>
-      <c r="AE19" s="53"/>
-      <c r="AF19" s="53"/>
-      <c r="AG19" s="53"/>
-      <c r="AH19" s="53"/>
-      <c r="AI19" s="53"/>
-      <c r="AJ19" s="53"/>
-      <c r="AK19" s="53"/>
-      <c r="AL19" s="53"/>
-      <c r="AM19" s="53"/>
-      <c r="AN19" s="53"/>
-      <c r="AO19" s="53"/>
-      <c r="AP19" s="53"/>
-      <c r="AQ19" s="53"/>
-      <c r="AR19" s="53"/>
-      <c r="AS19" s="53"/>
-      <c r="AT19" s="53"/>
-      <c r="AU19" s="53"/>
-      <c r="AV19" s="53"/>
-      <c r="AW19" s="53"/>
-      <c r="AX19" s="53"/>
-      <c r="AY19" s="53"/>
-      <c r="AZ19" s="53"/>
-      <c r="BA19" s="53"/>
-      <c r="BB19" s="53"/>
-      <c r="BC19" s="53"/>
-      <c r="BD19" s="53"/>
-      <c r="BE19" s="53"/>
-      <c r="BF19" s="53"/>
-      <c r="BG19" s="53"/>
-      <c r="BH19" s="53"/>
-      <c r="BI19" s="53"/>
-    </row>
-    <row r="20" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="53"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="53"/>
-      <c r="U20" s="53"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="53"/>
-      <c r="AB20" s="53"/>
-      <c r="AC20" s="53"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="53"/>
-      <c r="AF20" s="53"/>
-      <c r="AG20" s="53"/>
-      <c r="AH20" s="53"/>
-      <c r="AI20" s="53"/>
-      <c r="AJ20" s="53"/>
-      <c r="AK20" s="53"/>
-      <c r="AL20" s="53"/>
-      <c r="AM20" s="53"/>
-      <c r="AN20" s="53"/>
-      <c r="AO20" s="53"/>
-      <c r="AP20" s="53"/>
-      <c r="AQ20" s="53"/>
-      <c r="AR20" s="53"/>
-      <c r="AS20" s="53"/>
-      <c r="AT20" s="53"/>
-      <c r="AU20" s="53"/>
-      <c r="AV20" s="53"/>
-      <c r="AW20" s="53"/>
-      <c r="AX20" s="53"/>
-      <c r="AY20" s="53"/>
-      <c r="AZ20" s="53"/>
-      <c r="BA20" s="53"/>
-      <c r="BB20" s="53"/>
-      <c r="BC20" s="53"/>
-      <c r="BD20" s="53"/>
-      <c r="BE20" s="53"/>
-      <c r="BF20" s="53"/>
-      <c r="BG20" s="53"/>
-      <c r="BH20" s="53"/>
-      <c r="BI20" s="53"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="37"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="37"/>
+      <c r="Y20" s="37"/>
+      <c r="Z20" s="37"/>
+      <c r="AA20" s="37"/>
+      <c r="AB20" s="37"/>
+      <c r="AC20" s="37"/>
+      <c r="AD20" s="37"/>
+      <c r="AE20" s="37"/>
+      <c r="AF20" s="37"/>
+      <c r="AG20" s="37"/>
+      <c r="AH20" s="37"/>
+      <c r="AI20" s="37"/>
+      <c r="AJ20" s="37"/>
+      <c r="AK20" s="37"/>
+      <c r="AL20" s="37"/>
+      <c r="AM20" s="37"/>
+      <c r="AN20" s="37"/>
+      <c r="AO20" s="37"/>
+      <c r="AP20" s="37"/>
+      <c r="AQ20" s="37"/>
+      <c r="AR20" s="37"/>
+      <c r="AS20" s="37"/>
+      <c r="AT20" s="37"/>
+      <c r="AU20" s="37"/>
+      <c r="AV20" s="37"/>
+      <c r="AW20" s="37"/>
+      <c r="AX20" s="37"/>
+      <c r="AY20" s="37"/>
+      <c r="AZ20" s="37"/>
+      <c r="BA20" s="37"/>
+      <c r="BB20" s="37"/>
+      <c r="BC20" s="37"/>
+      <c r="BD20" s="37"/>
+      <c r="BE20" s="37"/>
+      <c r="BF20" s="37"/>
+      <c r="BG20" s="37"/>
+      <c r="BH20" s="37"/>
+      <c r="BI20" s="37"/>
     </row>
     <row r="21" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="53"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="53"/>
-      <c r="U21" s="53"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="53"/>
-      <c r="Z21" s="53"/>
-      <c r="AA21" s="53"/>
-      <c r="AB21" s="53"/>
-      <c r="AC21" s="53"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="53"/>
-      <c r="AF21" s="53"/>
-      <c r="AG21" s="53"/>
-      <c r="AH21" s="53"/>
-      <c r="AI21" s="53"/>
-      <c r="AJ21" s="53"/>
-      <c r="AK21" s="53"/>
-      <c r="AL21" s="53"/>
-      <c r="AM21" s="53"/>
-      <c r="AN21" s="53"/>
-      <c r="AO21" s="53"/>
-      <c r="AP21" s="53"/>
-      <c r="AQ21" s="53"/>
-      <c r="AR21" s="53"/>
-      <c r="AS21" s="53"/>
-      <c r="AT21" s="53"/>
-      <c r="AU21" s="53"/>
-      <c r="AV21" s="53"/>
-      <c r="AW21" s="53"/>
-      <c r="AX21" s="53"/>
-      <c r="AY21" s="53"/>
-      <c r="AZ21" s="53"/>
-      <c r="BA21" s="53"/>
-      <c r="BB21" s="53"/>
-      <c r="BC21" s="53"/>
-      <c r="BD21" s="53"/>
-      <c r="BE21" s="53"/>
-      <c r="BF21" s="53"/>
-      <c r="BG21" s="53"/>
-      <c r="BH21" s="53"/>
-      <c r="BI21" s="53"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="37"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="37"/>
+      <c r="Y21" s="37"/>
+      <c r="Z21" s="37"/>
+      <c r="AA21" s="37"/>
+      <c r="AB21" s="37"/>
+      <c r="AC21" s="37"/>
+      <c r="AD21" s="37"/>
+      <c r="AE21" s="37"/>
+      <c r="AF21" s="37"/>
+      <c r="AG21" s="37"/>
+      <c r="AH21" s="37"/>
+      <c r="AI21" s="37"/>
+      <c r="AJ21" s="37"/>
+      <c r="AK21" s="37"/>
+      <c r="AL21" s="37"/>
+      <c r="AM21" s="37"/>
+      <c r="AN21" s="37"/>
+      <c r="AO21" s="37"/>
+      <c r="AP21" s="37"/>
+      <c r="AQ21" s="37"/>
+      <c r="AR21" s="37"/>
+      <c r="AS21" s="37"/>
+      <c r="AT21" s="37"/>
+      <c r="AU21" s="37"/>
+      <c r="AV21" s="37"/>
+      <c r="AW21" s="37"/>
+      <c r="AX21" s="37"/>
+      <c r="AY21" s="37"/>
+      <c r="AZ21" s="37"/>
+      <c r="BA21" s="37"/>
+      <c r="BB21" s="37"/>
+      <c r="BC21" s="37"/>
+      <c r="BD21" s="37"/>
+      <c r="BE21" s="37"/>
+      <c r="BF21" s="37"/>
+      <c r="BG21" s="37"/>
+      <c r="BH21" s="37"/>
+      <c r="BI21" s="37"/>
     </row>
     <row r="22" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="53"/>
-      <c r="W22" s="53"/>
-      <c r="X22" s="53"/>
-      <c r="Y22" s="53"/>
-      <c r="Z22" s="53"/>
-      <c r="AA22" s="53"/>
-      <c r="AB22" s="53"/>
-      <c r="AC22" s="53"/>
-      <c r="AD22" s="53"/>
-      <c r="AE22" s="53"/>
-      <c r="AF22" s="53"/>
-      <c r="AG22" s="53"/>
-      <c r="AH22" s="53"/>
-      <c r="AI22" s="53"/>
-      <c r="AJ22" s="53"/>
-      <c r="AK22" s="53"/>
-      <c r="AL22" s="53"/>
-      <c r="AM22" s="53"/>
-      <c r="AN22" s="53"/>
-      <c r="AO22" s="53"/>
-      <c r="AP22" s="53"/>
-      <c r="AQ22" s="53"/>
-      <c r="AR22" s="53"/>
-      <c r="AS22" s="53"/>
-      <c r="AT22" s="53"/>
-      <c r="AU22" s="53"/>
-      <c r="AV22" s="53"/>
-      <c r="AW22" s="53"/>
-      <c r="AX22" s="53"/>
-      <c r="AY22" s="53"/>
-      <c r="AZ22" s="53"/>
-      <c r="BA22" s="53"/>
-      <c r="BB22" s="53"/>
-      <c r="BC22" s="53"/>
-      <c r="BD22" s="53"/>
-      <c r="BE22" s="53"/>
-      <c r="BF22" s="53"/>
-      <c r="BG22" s="53"/>
-      <c r="BH22" s="53"/>
-      <c r="BI22" s="53"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="37"/>
+      <c r="U22" s="37"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="37"/>
+      <c r="Y22" s="37"/>
+      <c r="Z22" s="37"/>
+      <c r="AA22" s="37"/>
+      <c r="AB22" s="37"/>
+      <c r="AC22" s="37"/>
+      <c r="AD22" s="37"/>
+      <c r="AE22" s="37"/>
+      <c r="AF22" s="37"/>
+      <c r="AG22" s="37"/>
+      <c r="AH22" s="37"/>
+      <c r="AI22" s="37"/>
+      <c r="AJ22" s="37"/>
+      <c r="AK22" s="37"/>
+      <c r="AL22" s="37"/>
+      <c r="AM22" s="37"/>
+      <c r="AN22" s="37"/>
+      <c r="AO22" s="37"/>
+      <c r="AP22" s="37"/>
+      <c r="AQ22" s="37"/>
+      <c r="AR22" s="37"/>
+      <c r="AS22" s="37"/>
+      <c r="AT22" s="37"/>
+      <c r="AU22" s="37"/>
+      <c r="AV22" s="37"/>
+      <c r="AW22" s="37"/>
+      <c r="AX22" s="37"/>
+      <c r="AY22" s="37"/>
+      <c r="AZ22" s="37"/>
+      <c r="BA22" s="37"/>
+      <c r="BB22" s="37"/>
+      <c r="BC22" s="37"/>
+      <c r="BD22" s="37"/>
+      <c r="BE22" s="37"/>
+      <c r="BF22" s="37"/>
+      <c r="BG22" s="37"/>
+      <c r="BH22" s="37"/>
+      <c r="BI22" s="37"/>
     </row>
     <row r="23" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="53"/>
-      <c r="T23" s="53"/>
-      <c r="U23" s="53"/>
-      <c r="V23" s="53"/>
-      <c r="W23" s="53"/>
-      <c r="X23" s="53"/>
-      <c r="Y23" s="53"/>
-      <c r="Z23" s="53"/>
-      <c r="AA23" s="53"/>
-      <c r="AB23" s="53"/>
-      <c r="AC23" s="53"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="53"/>
-      <c r="AF23" s="53"/>
-      <c r="AG23" s="53"/>
-      <c r="AH23" s="53"/>
-      <c r="AI23" s="53"/>
-      <c r="AJ23" s="53"/>
-      <c r="AK23" s="53"/>
-      <c r="AL23" s="53"/>
-      <c r="AM23" s="53"/>
-      <c r="AN23" s="53"/>
-      <c r="AO23" s="53"/>
-      <c r="AP23" s="53"/>
-      <c r="AQ23" s="53"/>
-      <c r="AR23" s="53"/>
-      <c r="AS23" s="53"/>
-      <c r="AT23" s="53"/>
-      <c r="AU23" s="53"/>
-      <c r="AV23" s="53"/>
-      <c r="AW23" s="53"/>
-      <c r="AX23" s="53"/>
-      <c r="AY23" s="53"/>
-      <c r="AZ23" s="53"/>
-      <c r="BA23" s="53"/>
-      <c r="BB23" s="53"/>
-      <c r="BC23" s="53"/>
-      <c r="BD23" s="53"/>
-      <c r="BE23" s="53"/>
-      <c r="BF23" s="53"/>
-      <c r="BG23" s="53"/>
-      <c r="BH23" s="53"/>
-      <c r="BI23" s="53"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="37"/>
+      <c r="AA23" s="37"/>
+      <c r="AB23" s="37"/>
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="37"/>
+      <c r="AE23" s="37"/>
+      <c r="AF23" s="37"/>
+      <c r="AG23" s="37"/>
+      <c r="AH23" s="37"/>
+      <c r="AI23" s="37"/>
+      <c r="AJ23" s="37"/>
+      <c r="AK23" s="37"/>
+      <c r="AL23" s="37"/>
+      <c r="AM23" s="37"/>
+      <c r="AN23" s="37"/>
+      <c r="AO23" s="37"/>
+      <c r="AP23" s="37"/>
+      <c r="AQ23" s="37"/>
+      <c r="AR23" s="37"/>
+      <c r="AS23" s="37"/>
+      <c r="AT23" s="37"/>
+      <c r="AU23" s="37"/>
+      <c r="AV23" s="37"/>
+      <c r="AW23" s="37"/>
+      <c r="AX23" s="37"/>
+      <c r="AY23" s="37"/>
+      <c r="AZ23" s="37"/>
+      <c r="BA23" s="37"/>
+      <c r="BB23" s="37"/>
+      <c r="BC23" s="37"/>
+      <c r="BD23" s="37"/>
+      <c r="BE23" s="37"/>
+      <c r="BF23" s="37"/>
+      <c r="BG23" s="37"/>
+      <c r="BH23" s="37"/>
+      <c r="BI23" s="37"/>
     </row>
     <row r="24" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="53"/>
-      <c r="T24" s="53"/>
-      <c r="U24" s="53"/>
-      <c r="V24" s="53"/>
-      <c r="W24" s="53"/>
-      <c r="X24" s="53"/>
-      <c r="Y24" s="53"/>
-      <c r="Z24" s="53"/>
-      <c r="AA24" s="53"/>
-      <c r="AB24" s="53"/>
-      <c r="AC24" s="53"/>
-      <c r="AD24" s="53"/>
-      <c r="AE24" s="53"/>
-      <c r="AF24" s="53"/>
-      <c r="AG24" s="53"/>
-      <c r="AH24" s="53"/>
-      <c r="AI24" s="53"/>
-      <c r="AJ24" s="53"/>
-      <c r="AK24" s="53"/>
-      <c r="AL24" s="53"/>
-      <c r="AM24" s="53"/>
-      <c r="AN24" s="53"/>
-      <c r="AO24" s="53"/>
-      <c r="AP24" s="53"/>
-      <c r="AQ24" s="53"/>
-      <c r="AR24" s="53"/>
-      <c r="AS24" s="53"/>
-      <c r="AT24" s="53"/>
-      <c r="AU24" s="53"/>
-      <c r="AV24" s="53"/>
-      <c r="AW24" s="53"/>
-      <c r="AX24" s="53"/>
-      <c r="AY24" s="53"/>
-      <c r="AZ24" s="53"/>
-      <c r="BA24" s="53"/>
-      <c r="BB24" s="53"/>
-      <c r="BC24" s="53"/>
-      <c r="BD24" s="53"/>
-      <c r="BE24" s="53"/>
-      <c r="BF24" s="53"/>
-      <c r="BG24" s="53"/>
-      <c r="BH24" s="53"/>
-      <c r="BI24" s="53"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="37"/>
+      <c r="Y24" s="37"/>
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="37"/>
+      <c r="AE24" s="37"/>
+      <c r="AF24" s="37"/>
+      <c r="AG24" s="37"/>
+      <c r="AH24" s="37"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="37"/>
+      <c r="AK24" s="37"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="37"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="37"/>
+      <c r="AQ24" s="37"/>
+      <c r="AR24" s="37"/>
+      <c r="AS24" s="37"/>
+      <c r="AT24" s="37"/>
+      <c r="AU24" s="37"/>
+      <c r="AV24" s="37"/>
+      <c r="AW24" s="37"/>
+      <c r="AX24" s="37"/>
+      <c r="AY24" s="37"/>
+      <c r="AZ24" s="37"/>
+      <c r="BA24" s="37"/>
+      <c r="BB24" s="37"/>
+      <c r="BC24" s="37"/>
+      <c r="BD24" s="37"/>
+      <c r="BE24" s="37"/>
+      <c r="BF24" s="37"/>
+      <c r="BG24" s="37"/>
+      <c r="BH24" s="37"/>
+      <c r="BI24" s="37"/>
+    </row>
+    <row r="25" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="37"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
+      <c r="S25" s="37"/>
+      <c r="T25" s="37"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="37"/>
+      <c r="Z25" s="37"/>
+      <c r="AA25" s="37"/>
+      <c r="AB25" s="37"/>
+      <c r="AC25" s="37"/>
+      <c r="AD25" s="37"/>
+      <c r="AE25" s="37"/>
+      <c r="AF25" s="37"/>
+      <c r="AG25" s="37"/>
+      <c r="AH25" s="37"/>
+      <c r="AI25" s="37"/>
+      <c r="AJ25" s="37"/>
+      <c r="AK25" s="37"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="37"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="37"/>
+      <c r="AQ25" s="37"/>
+      <c r="AR25" s="37"/>
+      <c r="AS25" s="37"/>
+      <c r="AT25" s="37"/>
+      <c r="AU25" s="37"/>
+      <c r="AV25" s="37"/>
+      <c r="AW25" s="37"/>
+      <c r="AX25" s="37"/>
+      <c r="AY25" s="37"/>
+      <c r="AZ25" s="37"/>
+      <c r="BA25" s="37"/>
+      <c r="BB25" s="37"/>
+      <c r="BC25" s="37"/>
+      <c r="BD25" s="37"/>
+      <c r="BE25" s="37"/>
+      <c r="BF25" s="37"/>
+      <c r="BG25" s="37"/>
+      <c r="BH25" s="37"/>
+      <c r="BI25" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A19:BI24"/>
-    <mergeCell ref="A18:BI18"/>
-    <mergeCell ref="A15:P15"/>
-    <mergeCell ref="Q15:X15"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A14:P14"/>
-    <mergeCell ref="Q14:X14"/>
-    <mergeCell ref="A13:P13"/>
-    <mergeCell ref="Q13:X13"/>
-    <mergeCell ref="A12:P12"/>
+  <mergeCells count="45">
     <mergeCell ref="Q12:X12"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="Q11:X11"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="A9:P9"/>
+    <mergeCell ref="Q9:X9"/>
     <mergeCell ref="BD1:BI1"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="AE1:AP1"/>
@@ -3176,14 +3235,28 @@
     <mergeCell ref="G5:BI5"/>
     <mergeCell ref="G6:AE6"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="A9:P9"/>
-    <mergeCell ref="Q9:X9"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="A20:BI25"/>
+    <mergeCell ref="A19:BI19"/>
+    <mergeCell ref="A16:P16"/>
+    <mergeCell ref="Q16:X16"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A15:P15"/>
+    <mergeCell ref="Q15:X15"/>
+    <mergeCell ref="A14:P14"/>
+    <mergeCell ref="Q14:X14"/>
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="Q13:X13"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="Q11:X11"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="Q10:X10"/>
+    <mergeCell ref="A12:P12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3202,83 +3275,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="37" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="38" t="s">
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="37" t="s">
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
-      <c r="AP1" s="38"/>
-      <c r="AQ1" s="37" t="s">
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="38" t="s">
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="38"/>
-      <c r="AX1" s="38"/>
-      <c r="AY1" s="38"/>
-      <c r="AZ1" s="38"/>
-      <c r="BA1" s="37" t="s">
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="42">
+      <c r="BB1" s="51"/>
+      <c r="BC1" s="51"/>
+      <c r="BD1" s="52">
         <v>45554</v>
       </c>
-      <c r="BE1" s="42"/>
-      <c r="BF1" s="42"/>
-      <c r="BG1" s="42"/>
-      <c r="BH1" s="42"/>
-      <c r="BI1" s="42"/>
+      <c r="BE1" s="52"/>
+      <c r="BF1" s="52"/>
+      <c r="BG1" s="52"/>
+      <c r="BH1" s="52"/>
+      <c r="BI1" s="52"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3478,77 +3551,77 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="37" t="s">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="37" t="s">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="38" t="s">
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="37" t="s">
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="37"/>
-      <c r="AS2" s="37"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="38"/>
-      <c r="AX2" s="38"/>
-      <c r="AY2" s="38"/>
-      <c r="AZ2" s="38"/>
-      <c r="BA2" s="37" t="s">
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="37"/>
-      <c r="BC2" s="37"/>
-      <c r="BD2" s="42"/>
-      <c r="BE2" s="42"/>
-      <c r="BF2" s="42"/>
-      <c r="BG2" s="42"/>
-      <c r="BH2" s="42"/>
-      <c r="BI2" s="42"/>
+      <c r="BB2" s="51"/>
+      <c r="BC2" s="51"/>
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3748,71 +3821,71 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="52" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="52"/>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="52"/>
-      <c r="AK4" s="52"/>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="52"/>
-      <c r="AN4" s="52"/>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="52"/>
-      <c r="AQ4" s="52"/>
-      <c r="AR4" s="52"/>
-      <c r="AS4" s="52"/>
-      <c r="AT4" s="52"/>
-      <c r="AU4" s="52"/>
-      <c r="AV4" s="52"/>
-      <c r="AW4" s="52"/>
-      <c r="AX4" s="52"/>
-      <c r="AY4" s="52"/>
-      <c r="AZ4" s="52"/>
-      <c r="BA4" s="52"/>
-      <c r="BB4" s="52"/>
-      <c r="BC4" s="52"/>
-      <c r="BD4" s="52"/>
-      <c r="BE4" s="52"/>
-      <c r="BF4" s="52"/>
-      <c r="BG4" s="52"/>
-      <c r="BH4" s="52"/>
-      <c r="BI4" s="52"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -4012,71 +4085,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="48" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="48"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="48"/>
-      <c r="AY5" s="48"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="48"/>
-      <c r="BD5" s="48"/>
-      <c r="BE5" s="48"/>
-      <c r="BF5" s="48"/>
-      <c r="BG5" s="48"/>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="48"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="57"/>
+      <c r="AB5" s="57"/>
+      <c r="AC5" s="57"/>
+      <c r="AD5" s="57"/>
+      <c r="AE5" s="57"/>
+      <c r="AF5" s="57"/>
+      <c r="AG5" s="57"/>
+      <c r="AH5" s="57"/>
+      <c r="AI5" s="57"/>
+      <c r="AJ5" s="57"/>
+      <c r="AK5" s="57"/>
+      <c r="AL5" s="57"/>
+      <c r="AM5" s="57"/>
+      <c r="AN5" s="57"/>
+      <c r="AO5" s="57"/>
+      <c r="AP5" s="57"/>
+      <c r="AQ5" s="57"/>
+      <c r="AR5" s="57"/>
+      <c r="AS5" s="57"/>
+      <c r="AT5" s="57"/>
+      <c r="AU5" s="57"/>
+      <c r="AV5" s="57"/>
+      <c r="AW5" s="57"/>
+      <c r="AX5" s="57"/>
+      <c r="AY5" s="57"/>
+      <c r="AZ5" s="57"/>
+      <c r="BA5" s="57"/>
+      <c r="BB5" s="57"/>
+      <c r="BC5" s="57"/>
+      <c r="BD5" s="57"/>
+      <c r="BE5" s="57"/>
+      <c r="BF5" s="57"/>
+      <c r="BG5" s="57"/>
+      <c r="BH5" s="57"/>
+      <c r="BI5" s="57"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4536,75 +4609,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58" t="s">
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="58"/>
-      <c r="AA7" s="58"/>
-      <c r="AB7" s="58"/>
-      <c r="AC7" s="58"/>
-      <c r="AD7" s="58"/>
-      <c r="AE7" s="58" t="s">
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="64"/>
+      <c r="AB7" s="64"/>
+      <c r="AC7" s="64"/>
+      <c r="AD7" s="64"/>
+      <c r="AE7" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="AF7" s="58"/>
-      <c r="AG7" s="58"/>
-      <c r="AH7" s="58"/>
-      <c r="AI7" s="58"/>
-      <c r="AJ7" s="58"/>
-      <c r="AK7" s="58"/>
-      <c r="AL7" s="58"/>
-      <c r="AM7" s="58"/>
-      <c r="AN7" s="58"/>
-      <c r="AO7" s="58"/>
-      <c r="AP7" s="58"/>
-      <c r="AQ7" s="58"/>
-      <c r="AR7" s="58"/>
-      <c r="AS7" s="58"/>
-      <c r="AT7" s="58"/>
-      <c r="AU7" s="58"/>
-      <c r="AV7" s="58"/>
-      <c r="AW7" s="58"/>
-      <c r="AX7" s="58"/>
-      <c r="AY7" s="58"/>
-      <c r="AZ7" s="58"/>
-      <c r="BA7" s="58"/>
-      <c r="BB7" s="58"/>
-      <c r="BC7" s="58"/>
-      <c r="BD7" s="58"/>
-      <c r="BE7" s="58"/>
-      <c r="BF7" s="58"/>
-      <c r="BG7" s="58"/>
-      <c r="BH7" s="58"/>
-      <c r="BI7" s="58"/>
+      <c r="AF7" s="64"/>
+      <c r="AG7" s="64"/>
+      <c r="AH7" s="64"/>
+      <c r="AI7" s="64"/>
+      <c r="AJ7" s="64"/>
+      <c r="AK7" s="64"/>
+      <c r="AL7" s="64"/>
+      <c r="AM7" s="64"/>
+      <c r="AN7" s="64"/>
+      <c r="AO7" s="64"/>
+      <c r="AP7" s="64"/>
+      <c r="AQ7" s="64"/>
+      <c r="AR7" s="64"/>
+      <c r="AS7" s="64"/>
+      <c r="AT7" s="64"/>
+      <c r="AU7" s="64"/>
+      <c r="AV7" s="64"/>
+      <c r="AW7" s="64"/>
+      <c r="AX7" s="64"/>
+      <c r="AY7" s="64"/>
+      <c r="AZ7" s="64"/>
+      <c r="BA7" s="64"/>
+      <c r="BB7" s="64"/>
+      <c r="BC7" s="64"/>
+      <c r="BD7" s="64"/>
+      <c r="BE7" s="64"/>
+      <c r="BF7" s="64"/>
+      <c r="BG7" s="64"/>
+      <c r="BH7" s="64"/>
+      <c r="BI7" s="64"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4804,73 +4877,73 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="57"/>
-      <c r="P8" s="57" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="57"/>
-      <c r="R8" s="57"/>
-      <c r="S8" s="57"/>
-      <c r="T8" s="57"/>
-      <c r="U8" s="57"/>
-      <c r="V8" s="57"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="57"/>
-      <c r="Y8" s="57"/>
-      <c r="Z8" s="57"/>
-      <c r="AA8" s="57"/>
-      <c r="AB8" s="57"/>
-      <c r="AC8" s="57"/>
-      <c r="AD8" s="57"/>
-      <c r="AE8" s="57" t="s">
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AF8" s="57"/>
-      <c r="AG8" s="57"/>
-      <c r="AH8" s="57"/>
-      <c r="AI8" s="57"/>
-      <c r="AJ8" s="57"/>
-      <c r="AK8" s="57"/>
-      <c r="AL8" s="57"/>
-      <c r="AM8" s="57"/>
-      <c r="AN8" s="57"/>
-      <c r="AO8" s="57"/>
-      <c r="AP8" s="57"/>
-      <c r="AQ8" s="57"/>
-      <c r="AR8" s="57"/>
-      <c r="AS8" s="57"/>
-      <c r="AT8" s="57"/>
-      <c r="AU8" s="57"/>
-      <c r="AV8" s="57"/>
-      <c r="AW8" s="57"/>
-      <c r="AX8" s="57"/>
-      <c r="AY8" s="57"/>
-      <c r="AZ8" s="57"/>
-      <c r="BA8" s="57"/>
-      <c r="BB8" s="57"/>
-      <c r="BC8" s="57"/>
-      <c r="BD8" s="57"/>
-      <c r="BE8" s="57"/>
-      <c r="BF8" s="57"/>
-      <c r="BG8" s="57"/>
-      <c r="BH8" s="57"/>
-      <c r="BI8" s="57"/>
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="71"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="71"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="71"/>
+      <c r="AO8" s="71"/>
+      <c r="AP8" s="71"/>
+      <c r="AQ8" s="71"/>
+      <c r="AR8" s="71"/>
+      <c r="AS8" s="71"/>
+      <c r="AT8" s="71"/>
+      <c r="AU8" s="71"/>
+      <c r="AV8" s="71"/>
+      <c r="AW8" s="71"/>
+      <c r="AX8" s="71"/>
+      <c r="AY8" s="71"/>
+      <c r="AZ8" s="71"/>
+      <c r="BA8" s="71"/>
+      <c r="BB8" s="71"/>
+      <c r="BC8" s="71"/>
+      <c r="BD8" s="71"/>
+      <c r="BE8" s="71"/>
+      <c r="BF8" s="71"/>
+      <c r="BG8" s="71"/>
+      <c r="BH8" s="71"/>
+      <c r="BI8" s="71"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -5070,67 +5143,67 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="60"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="60"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="60"/>
-      <c r="AD9" s="60"/>
-      <c r="AE9" s="60"/>
-      <c r="AF9" s="60"/>
-      <c r="AG9" s="60"/>
-      <c r="AH9" s="60"/>
-      <c r="AI9" s="60"/>
-      <c r="AJ9" s="60"/>
-      <c r="AK9" s="60"/>
-      <c r="AL9" s="60"/>
-      <c r="AM9" s="60"/>
-      <c r="AN9" s="60"/>
-      <c r="AO9" s="60"/>
-      <c r="AP9" s="60"/>
-      <c r="AQ9" s="60"/>
-      <c r="AR9" s="60"/>
-      <c r="AS9" s="60"/>
-      <c r="AT9" s="60"/>
-      <c r="AU9" s="60"/>
-      <c r="AV9" s="60"/>
-      <c r="AW9" s="60"/>
-      <c r="AX9" s="60"/>
-      <c r="AY9" s="60"/>
-      <c r="AZ9" s="60"/>
-      <c r="BA9" s="60"/>
-      <c r="BB9" s="60"/>
-      <c r="BC9" s="60"/>
-      <c r="BD9" s="60"/>
-      <c r="BE9" s="60"/>
-      <c r="BF9" s="60"/>
-      <c r="BG9" s="60"/>
-      <c r="BH9" s="60"/>
-      <c r="BI9" s="60"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="63"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="63"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="63"/>
+      <c r="X9" s="63"/>
+      <c r="Y9" s="63"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="63"/>
+      <c r="AB9" s="63"/>
+      <c r="AC9" s="63"/>
+      <c r="AD9" s="63"/>
+      <c r="AE9" s="63"/>
+      <c r="AF9" s="63"/>
+      <c r="AG9" s="63"/>
+      <c r="AH9" s="63"/>
+      <c r="AI9" s="63"/>
+      <c r="AJ9" s="63"/>
+      <c r="AK9" s="63"/>
+      <c r="AL9" s="63"/>
+      <c r="AM9" s="63"/>
+      <c r="AN9" s="63"/>
+      <c r="AO9" s="63"/>
+      <c r="AP9" s="63"/>
+      <c r="AQ9" s="63"/>
+      <c r="AR9" s="63"/>
+      <c r="AS9" s="63"/>
+      <c r="AT9" s="63"/>
+      <c r="AU9" s="63"/>
+      <c r="AV9" s="63"/>
+      <c r="AW9" s="63"/>
+      <c r="AX9" s="63"/>
+      <c r="AY9" s="63"/>
+      <c r="AZ9" s="63"/>
+      <c r="BA9" s="63"/>
+      <c r="BB9" s="63"/>
+      <c r="BC9" s="63"/>
+      <c r="BD9" s="63"/>
+      <c r="BE9" s="63"/>
+      <c r="BF9" s="63"/>
+      <c r="BG9" s="63"/>
+      <c r="BH9" s="63"/>
+      <c r="BI9" s="63"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -5330,67 +5403,67 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="40"/>
-      <c r="Z10" s="40"/>
-      <c r="AA10" s="40"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="40"/>
-      <c r="AD10" s="40"/>
-      <c r="AE10" s="40"/>
-      <c r="AF10" s="40"/>
-      <c r="AG10" s="40"/>
-      <c r="AH10" s="40"/>
-      <c r="AI10" s="40"/>
-      <c r="AJ10" s="40"/>
-      <c r="AK10" s="40"/>
-      <c r="AL10" s="40"/>
-      <c r="AM10" s="40"/>
-      <c r="AN10" s="40"/>
-      <c r="AO10" s="40"/>
-      <c r="AP10" s="40"/>
-      <c r="AQ10" s="40"/>
-      <c r="AR10" s="40"/>
-      <c r="AS10" s="40"/>
-      <c r="AT10" s="40"/>
-      <c r="AU10" s="40"/>
-      <c r="AV10" s="40"/>
-      <c r="AW10" s="40"/>
-      <c r="AX10" s="40"/>
-      <c r="AY10" s="40"/>
-      <c r="AZ10" s="40"/>
-      <c r="BA10" s="40"/>
-      <c r="BB10" s="40"/>
-      <c r="BC10" s="40"/>
-      <c r="BD10" s="40"/>
-      <c r="BE10" s="40"/>
-      <c r="BF10" s="40"/>
-      <c r="BG10" s="40"/>
-      <c r="BH10" s="40"/>
-      <c r="BI10" s="40"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="60"/>
+      <c r="AA10" s="60"/>
+      <c r="AB10" s="60"/>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="60"/>
+      <c r="AE10" s="60"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+      <c r="BC10" s="60"/>
+      <c r="BD10" s="60"/>
+      <c r="BE10" s="60"/>
+      <c r="BF10" s="60"/>
+      <c r="BG10" s="60"/>
+      <c r="BH10" s="60"/>
+      <c r="BI10" s="60"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5590,67 +5663,67 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="40"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="40"/>
-      <c r="AP11" s="40"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="40"/>
-      <c r="AS11" s="40"/>
-      <c r="AT11" s="40"/>
-      <c r="AU11" s="40"/>
-      <c r="AV11" s="40"/>
-      <c r="AW11" s="40"/>
-      <c r="AX11" s="40"/>
-      <c r="AY11" s="40"/>
-      <c r="AZ11" s="40"/>
-      <c r="BA11" s="40"/>
-      <c r="BB11" s="40"/>
-      <c r="BC11" s="40"/>
-      <c r="BD11" s="40"/>
-      <c r="BE11" s="40"/>
-      <c r="BF11" s="40"/>
-      <c r="BG11" s="40"/>
-      <c r="BH11" s="40"/>
-      <c r="BI11" s="40"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="60"/>
+      <c r="O11" s="60"/>
+      <c r="P11" s="60"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="60"/>
+      <c r="S11" s="60"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="60"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="60"/>
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="60"/>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+      <c r="BC11" s="60"/>
+      <c r="BD11" s="60"/>
+      <c r="BE11" s="60"/>
+      <c r="BF11" s="60"/>
+      <c r="BG11" s="60"/>
+      <c r="BH11" s="60"/>
+      <c r="BI11" s="60"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -6370,75 +6443,75 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="63" t="s">
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="Q14" s="64"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="64" t="s">
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="T14" s="64"/>
-      <c r="U14" s="64"/>
-      <c r="V14" s="64"/>
-      <c r="W14" s="64"/>
-      <c r="X14" s="64"/>
-      <c r="Y14" s="64"/>
-      <c r="Z14" s="64"/>
-      <c r="AA14" s="64"/>
-      <c r="AB14" s="64"/>
-      <c r="AC14" s="64"/>
-      <c r="AD14" s="64"/>
-      <c r="AE14" s="64"/>
-      <c r="AF14" s="64"/>
-      <c r="AG14" s="64"/>
-      <c r="AH14" s="64"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="64"/>
-      <c r="AK14" s="64"/>
-      <c r="AL14" s="64"/>
-      <c r="AM14" s="64"/>
-      <c r="AN14" s="64"/>
-      <c r="AO14" s="64"/>
-      <c r="AP14" s="64"/>
-      <c r="AQ14" s="64"/>
-      <c r="AR14" s="64"/>
-      <c r="AS14" s="66"/>
-      <c r="AT14" s="61" t="s">
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="68"/>
+      <c r="W14" s="68"/>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="68"/>
+      <c r="Z14" s="68"/>
+      <c r="AA14" s="68"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="68"/>
+      <c r="AD14" s="68"/>
+      <c r="AE14" s="68"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="68"/>
+      <c r="AH14" s="68"/>
+      <c r="AI14" s="68"/>
+      <c r="AJ14" s="68"/>
+      <c r="AK14" s="68"/>
+      <c r="AL14" s="68"/>
+      <c r="AM14" s="68"/>
+      <c r="AN14" s="68"/>
+      <c r="AO14" s="68"/>
+      <c r="AP14" s="68"/>
+      <c r="AQ14" s="68"/>
+      <c r="AR14" s="68"/>
+      <c r="AS14" s="70"/>
+      <c r="AT14" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="AU14" s="61"/>
-      <c r="AV14" s="61"/>
-      <c r="AW14" s="61"/>
-      <c r="AX14" s="61"/>
-      <c r="AY14" s="61"/>
-      <c r="AZ14" s="61"/>
-      <c r="BA14" s="61"/>
-      <c r="BB14" s="61"/>
-      <c r="BC14" s="61"/>
-      <c r="BD14" s="61"/>
-      <c r="BE14" s="61"/>
-      <c r="BF14" s="61"/>
-      <c r="BG14" s="61"/>
-      <c r="BH14" s="61"/>
-      <c r="BI14" s="62"/>
+      <c r="AU14" s="65"/>
+      <c r="AV14" s="65"/>
+      <c r="AW14" s="65"/>
+      <c r="AX14" s="65"/>
+      <c r="AY14" s="65"/>
+      <c r="AZ14" s="65"/>
+      <c r="BA14" s="65"/>
+      <c r="BB14" s="65"/>
+      <c r="BC14" s="65"/>
+      <c r="BD14" s="65"/>
+      <c r="BE14" s="65"/>
+      <c r="BF14" s="65"/>
+      <c r="BG14" s="65"/>
+      <c r="BH14" s="65"/>
+      <c r="BI14" s="66"/>
       <c r="BJ14" s="1"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
@@ -7742,6 +7815,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="BD1:BI1"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:BI5"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="BD2:BI2"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:O9"/>
     <mergeCell ref="P9:AD9"/>
@@ -7758,35 +7860,6 @@
     <mergeCell ref="AE11:BI11"/>
     <mergeCell ref="P14:R14"/>
     <mergeCell ref="S14:AS14"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:BI5"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="BD2:BI2"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="2">
@@ -7813,83 +7886,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="37" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="38" t="s">
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="37" t="s">
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
-      <c r="AP1" s="38"/>
-      <c r="AQ1" s="37" t="s">
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="38" t="s">
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="38"/>
-      <c r="AX1" s="38"/>
-      <c r="AY1" s="38"/>
-      <c r="AZ1" s="38"/>
-      <c r="BA1" s="37" t="s">
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="42">
+      <c r="BB1" s="51"/>
+      <c r="BC1" s="51"/>
+      <c r="BD1" s="52">
         <v>45554</v>
       </c>
-      <c r="BE1" s="42"/>
-      <c r="BF1" s="42"/>
-      <c r="BG1" s="42"/>
-      <c r="BH1" s="42"/>
-      <c r="BI1" s="42"/>
+      <c r="BE1" s="52"/>
+      <c r="BF1" s="52"/>
+      <c r="BG1" s="52"/>
+      <c r="BH1" s="52"/>
+      <c r="BI1" s="52"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -8089,77 +8162,77 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="37" t="s">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="37" t="s">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="38" t="s">
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="37" t="s">
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="37"/>
-      <c r="AS2" s="37"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="38"/>
-      <c r="AX2" s="38"/>
-      <c r="AY2" s="38"/>
-      <c r="AZ2" s="38"/>
-      <c r="BA2" s="37" t="s">
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="37"/>
-      <c r="BC2" s="37"/>
-      <c r="BD2" s="42"/>
-      <c r="BE2" s="42"/>
-      <c r="BF2" s="42"/>
-      <c r="BG2" s="42"/>
-      <c r="BH2" s="42"/>
-      <c r="BI2" s="42"/>
+      <c r="BB2" s="51"/>
+      <c r="BC2" s="51"/>
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -8359,71 +8432,71 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="52" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="52"/>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="52"/>
-      <c r="AK4" s="52"/>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="52"/>
-      <c r="AN4" s="52"/>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="52"/>
-      <c r="AQ4" s="52"/>
-      <c r="AR4" s="52"/>
-      <c r="AS4" s="52"/>
-      <c r="AT4" s="52"/>
-      <c r="AU4" s="52"/>
-      <c r="AV4" s="52"/>
-      <c r="AW4" s="52"/>
-      <c r="AX4" s="52"/>
-      <c r="AY4" s="52"/>
-      <c r="AZ4" s="52"/>
-      <c r="BA4" s="52"/>
-      <c r="BB4" s="52"/>
-      <c r="BC4" s="52"/>
-      <c r="BD4" s="52"/>
-      <c r="BE4" s="52"/>
-      <c r="BF4" s="52"/>
-      <c r="BG4" s="52"/>
-      <c r="BH4" s="52"/>
-      <c r="BI4" s="52"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -8623,71 +8696,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="48" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="48"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="48"/>
-      <c r="AY5" s="48"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="48"/>
-      <c r="BD5" s="48"/>
-      <c r="BE5" s="48"/>
-      <c r="BF5" s="48"/>
-      <c r="BG5" s="48"/>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="48"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="57"/>
+      <c r="AB5" s="57"/>
+      <c r="AC5" s="57"/>
+      <c r="AD5" s="57"/>
+      <c r="AE5" s="57"/>
+      <c r="AF5" s="57"/>
+      <c r="AG5" s="57"/>
+      <c r="AH5" s="57"/>
+      <c r="AI5" s="57"/>
+      <c r="AJ5" s="57"/>
+      <c r="AK5" s="57"/>
+      <c r="AL5" s="57"/>
+      <c r="AM5" s="57"/>
+      <c r="AN5" s="57"/>
+      <c r="AO5" s="57"/>
+      <c r="AP5" s="57"/>
+      <c r="AQ5" s="57"/>
+      <c r="AR5" s="57"/>
+      <c r="AS5" s="57"/>
+      <c r="AT5" s="57"/>
+      <c r="AU5" s="57"/>
+      <c r="AV5" s="57"/>
+      <c r="AW5" s="57"/>
+      <c r="AX5" s="57"/>
+      <c r="AY5" s="57"/>
+      <c r="AZ5" s="57"/>
+      <c r="BA5" s="57"/>
+      <c r="BB5" s="57"/>
+      <c r="BC5" s="57"/>
+      <c r="BD5" s="57"/>
+      <c r="BE5" s="57"/>
+      <c r="BF5" s="57"/>
+      <c r="BG5" s="57"/>
+      <c r="BH5" s="57"/>
+      <c r="BI5" s="57"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -9147,75 +9220,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58" t="s">
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="58"/>
-      <c r="AA7" s="58"/>
-      <c r="AB7" s="58"/>
-      <c r="AC7" s="58"/>
-      <c r="AD7" s="58"/>
-      <c r="AE7" s="58" t="s">
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="64"/>
+      <c r="AB7" s="64"/>
+      <c r="AC7" s="64"/>
+      <c r="AD7" s="64"/>
+      <c r="AE7" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="AF7" s="58"/>
-      <c r="AG7" s="58"/>
-      <c r="AH7" s="58"/>
-      <c r="AI7" s="58"/>
-      <c r="AJ7" s="58"/>
-      <c r="AK7" s="58"/>
-      <c r="AL7" s="58"/>
-      <c r="AM7" s="58"/>
-      <c r="AN7" s="58"/>
-      <c r="AO7" s="58"/>
-      <c r="AP7" s="58"/>
-      <c r="AQ7" s="58"/>
-      <c r="AR7" s="58"/>
-      <c r="AS7" s="58"/>
-      <c r="AT7" s="58"/>
-      <c r="AU7" s="58"/>
-      <c r="AV7" s="58"/>
-      <c r="AW7" s="58"/>
-      <c r="AX7" s="58"/>
-      <c r="AY7" s="58"/>
-      <c r="AZ7" s="58"/>
-      <c r="BA7" s="58"/>
-      <c r="BB7" s="58"/>
-      <c r="BC7" s="58"/>
-      <c r="BD7" s="58"/>
-      <c r="BE7" s="58"/>
-      <c r="BF7" s="58"/>
-      <c r="BG7" s="58"/>
-      <c r="BH7" s="58"/>
-      <c r="BI7" s="58"/>
+      <c r="AF7" s="64"/>
+      <c r="AG7" s="64"/>
+      <c r="AH7" s="64"/>
+      <c r="AI7" s="64"/>
+      <c r="AJ7" s="64"/>
+      <c r="AK7" s="64"/>
+      <c r="AL7" s="64"/>
+      <c r="AM7" s="64"/>
+      <c r="AN7" s="64"/>
+      <c r="AO7" s="64"/>
+      <c r="AP7" s="64"/>
+      <c r="AQ7" s="64"/>
+      <c r="AR7" s="64"/>
+      <c r="AS7" s="64"/>
+      <c r="AT7" s="64"/>
+      <c r="AU7" s="64"/>
+      <c r="AV7" s="64"/>
+      <c r="AW7" s="64"/>
+      <c r="AX7" s="64"/>
+      <c r="AY7" s="64"/>
+      <c r="AZ7" s="64"/>
+      <c r="BA7" s="64"/>
+      <c r="BB7" s="64"/>
+      <c r="BC7" s="64"/>
+      <c r="BD7" s="64"/>
+      <c r="BE7" s="64"/>
+      <c r="BF7" s="64"/>
+      <c r="BG7" s="64"/>
+      <c r="BH7" s="64"/>
+      <c r="BI7" s="64"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -9415,75 +9488,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="57" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="57"/>
-      <c r="P8" s="57" t="s">
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="57"/>
-      <c r="R8" s="57"/>
-      <c r="S8" s="57"/>
-      <c r="T8" s="57"/>
-      <c r="U8" s="57"/>
-      <c r="V8" s="57"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="57"/>
-      <c r="Y8" s="57"/>
-      <c r="Z8" s="57"/>
-      <c r="AA8" s="57"/>
-      <c r="AB8" s="57"/>
-      <c r="AC8" s="57"/>
-      <c r="AD8" s="57"/>
-      <c r="AE8" s="57" t="s">
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="AF8" s="57"/>
-      <c r="AG8" s="57"/>
-      <c r="AH8" s="57"/>
-      <c r="AI8" s="57"/>
-      <c r="AJ8" s="57"/>
-      <c r="AK8" s="57"/>
-      <c r="AL8" s="57"/>
-      <c r="AM8" s="57"/>
-      <c r="AN8" s="57"/>
-      <c r="AO8" s="57"/>
-      <c r="AP8" s="57"/>
-      <c r="AQ8" s="57"/>
-      <c r="AR8" s="57"/>
-      <c r="AS8" s="57"/>
-      <c r="AT8" s="57"/>
-      <c r="AU8" s="57"/>
-      <c r="AV8" s="57"/>
-      <c r="AW8" s="57"/>
-      <c r="AX8" s="57"/>
-      <c r="AY8" s="57"/>
-      <c r="AZ8" s="57"/>
-      <c r="BA8" s="57"/>
-      <c r="BB8" s="57"/>
-      <c r="BC8" s="57"/>
-      <c r="BD8" s="57"/>
-      <c r="BE8" s="57"/>
-      <c r="BF8" s="57"/>
-      <c r="BG8" s="57"/>
-      <c r="BH8" s="57"/>
-      <c r="BI8" s="57"/>
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="71"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="71"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="71"/>
+      <c r="AO8" s="71"/>
+      <c r="AP8" s="71"/>
+      <c r="AQ8" s="71"/>
+      <c r="AR8" s="71"/>
+      <c r="AS8" s="71"/>
+      <c r="AT8" s="71"/>
+      <c r="AU8" s="71"/>
+      <c r="AV8" s="71"/>
+      <c r="AW8" s="71"/>
+      <c r="AX8" s="71"/>
+      <c r="AY8" s="71"/>
+      <c r="AZ8" s="71"/>
+      <c r="BA8" s="71"/>
+      <c r="BB8" s="71"/>
+      <c r="BC8" s="71"/>
+      <c r="BD8" s="71"/>
+      <c r="BE8" s="71"/>
+      <c r="BF8" s="71"/>
+      <c r="BG8" s="71"/>
+      <c r="BH8" s="71"/>
+      <c r="BI8" s="71"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -9683,67 +9756,67 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="60"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="60"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="60"/>
-      <c r="AD9" s="60"/>
-      <c r="AE9" s="60"/>
-      <c r="AF9" s="60"/>
-      <c r="AG9" s="60"/>
-      <c r="AH9" s="60"/>
-      <c r="AI9" s="60"/>
-      <c r="AJ9" s="60"/>
-      <c r="AK9" s="60"/>
-      <c r="AL9" s="60"/>
-      <c r="AM9" s="60"/>
-      <c r="AN9" s="60"/>
-      <c r="AO9" s="60"/>
-      <c r="AP9" s="60"/>
-      <c r="AQ9" s="60"/>
-      <c r="AR9" s="60"/>
-      <c r="AS9" s="60"/>
-      <c r="AT9" s="60"/>
-      <c r="AU9" s="60"/>
-      <c r="AV9" s="60"/>
-      <c r="AW9" s="60"/>
-      <c r="AX9" s="60"/>
-      <c r="AY9" s="60"/>
-      <c r="AZ9" s="60"/>
-      <c r="BA9" s="60"/>
-      <c r="BB9" s="60"/>
-      <c r="BC9" s="60"/>
-      <c r="BD9" s="60"/>
-      <c r="BE9" s="60"/>
-      <c r="BF9" s="60"/>
-      <c r="BG9" s="60"/>
-      <c r="BH9" s="60"/>
-      <c r="BI9" s="60"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="63"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="63"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="63"/>
+      <c r="X9" s="63"/>
+      <c r="Y9" s="63"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="63"/>
+      <c r="AB9" s="63"/>
+      <c r="AC9" s="63"/>
+      <c r="AD9" s="63"/>
+      <c r="AE9" s="63"/>
+      <c r="AF9" s="63"/>
+      <c r="AG9" s="63"/>
+      <c r="AH9" s="63"/>
+      <c r="AI9" s="63"/>
+      <c r="AJ9" s="63"/>
+      <c r="AK9" s="63"/>
+      <c r="AL9" s="63"/>
+      <c r="AM9" s="63"/>
+      <c r="AN9" s="63"/>
+      <c r="AO9" s="63"/>
+      <c r="AP9" s="63"/>
+      <c r="AQ9" s="63"/>
+      <c r="AR9" s="63"/>
+      <c r="AS9" s="63"/>
+      <c r="AT9" s="63"/>
+      <c r="AU9" s="63"/>
+      <c r="AV9" s="63"/>
+      <c r="AW9" s="63"/>
+      <c r="AX9" s="63"/>
+      <c r="AY9" s="63"/>
+      <c r="AZ9" s="63"/>
+      <c r="BA9" s="63"/>
+      <c r="BB9" s="63"/>
+      <c r="BC9" s="63"/>
+      <c r="BD9" s="63"/>
+      <c r="BE9" s="63"/>
+      <c r="BF9" s="63"/>
+      <c r="BG9" s="63"/>
+      <c r="BH9" s="63"/>
+      <c r="BI9" s="63"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -9943,67 +10016,67 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="40"/>
-      <c r="Z10" s="40"/>
-      <c r="AA10" s="40"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="40"/>
-      <c r="AD10" s="40"/>
-      <c r="AE10" s="40"/>
-      <c r="AF10" s="40"/>
-      <c r="AG10" s="40"/>
-      <c r="AH10" s="40"/>
-      <c r="AI10" s="40"/>
-      <c r="AJ10" s="40"/>
-      <c r="AK10" s="40"/>
-      <c r="AL10" s="40"/>
-      <c r="AM10" s="40"/>
-      <c r="AN10" s="40"/>
-      <c r="AO10" s="40"/>
-      <c r="AP10" s="40"/>
-      <c r="AQ10" s="40"/>
-      <c r="AR10" s="40"/>
-      <c r="AS10" s="40"/>
-      <c r="AT10" s="40"/>
-      <c r="AU10" s="40"/>
-      <c r="AV10" s="40"/>
-      <c r="AW10" s="40"/>
-      <c r="AX10" s="40"/>
-      <c r="AY10" s="40"/>
-      <c r="AZ10" s="40"/>
-      <c r="BA10" s="40"/>
-      <c r="BB10" s="40"/>
-      <c r="BC10" s="40"/>
-      <c r="BD10" s="40"/>
-      <c r="BE10" s="40"/>
-      <c r="BF10" s="40"/>
-      <c r="BG10" s="40"/>
-      <c r="BH10" s="40"/>
-      <c r="BI10" s="40"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="60"/>
+      <c r="AA10" s="60"/>
+      <c r="AB10" s="60"/>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="60"/>
+      <c r="AE10" s="60"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+      <c r="BC10" s="60"/>
+      <c r="BD10" s="60"/>
+      <c r="BE10" s="60"/>
+      <c r="BF10" s="60"/>
+      <c r="BG10" s="60"/>
+      <c r="BH10" s="60"/>
+      <c r="BI10" s="60"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -10203,67 +10276,67 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="40"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="40"/>
-      <c r="AP11" s="40"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="40"/>
-      <c r="AS11" s="40"/>
-      <c r="AT11" s="40"/>
-      <c r="AU11" s="40"/>
-      <c r="AV11" s="40"/>
-      <c r="AW11" s="40"/>
-      <c r="AX11" s="40"/>
-      <c r="AY11" s="40"/>
-      <c r="AZ11" s="40"/>
-      <c r="BA11" s="40"/>
-      <c r="BB11" s="40"/>
-      <c r="BC11" s="40"/>
-      <c r="BD11" s="40"/>
-      <c r="BE11" s="40"/>
-      <c r="BF11" s="40"/>
-      <c r="BG11" s="40"/>
-      <c r="BH11" s="40"/>
-      <c r="BI11" s="40"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="60"/>
+      <c r="O11" s="60"/>
+      <c r="P11" s="60"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="60"/>
+      <c r="S11" s="60"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="60"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="60"/>
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="60"/>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+      <c r="BC11" s="60"/>
+      <c r="BD11" s="60"/>
+      <c r="BE11" s="60"/>
+      <c r="BF11" s="60"/>
+      <c r="BG11" s="60"/>
+      <c r="BH11" s="60"/>
+      <c r="BI11" s="60"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -10983,75 +11056,75 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="63" t="s">
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="Q14" s="64"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="64" t="s">
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="T14" s="64"/>
-      <c r="U14" s="64"/>
-      <c r="V14" s="64"/>
-      <c r="W14" s="64"/>
-      <c r="X14" s="64"/>
-      <c r="Y14" s="64"/>
-      <c r="Z14" s="64"/>
-      <c r="AA14" s="64"/>
-      <c r="AB14" s="64"/>
-      <c r="AC14" s="64"/>
-      <c r="AD14" s="64"/>
-      <c r="AE14" s="64"/>
-      <c r="AF14" s="64"/>
-      <c r="AG14" s="64"/>
-      <c r="AH14" s="64"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="64"/>
-      <c r="AK14" s="64"/>
-      <c r="AL14" s="64"/>
-      <c r="AM14" s="64"/>
-      <c r="AN14" s="64"/>
-      <c r="AO14" s="64"/>
-      <c r="AP14" s="64"/>
-      <c r="AQ14" s="64"/>
-      <c r="AR14" s="64"/>
-      <c r="AS14" s="66"/>
-      <c r="AT14" s="61" t="s">
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="68"/>
+      <c r="W14" s="68"/>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="68"/>
+      <c r="Z14" s="68"/>
+      <c r="AA14" s="68"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="68"/>
+      <c r="AD14" s="68"/>
+      <c r="AE14" s="68"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="68"/>
+      <c r="AH14" s="68"/>
+      <c r="AI14" s="68"/>
+      <c r="AJ14" s="68"/>
+      <c r="AK14" s="68"/>
+      <c r="AL14" s="68"/>
+      <c r="AM14" s="68"/>
+      <c r="AN14" s="68"/>
+      <c r="AO14" s="68"/>
+      <c r="AP14" s="68"/>
+      <c r="AQ14" s="68"/>
+      <c r="AR14" s="68"/>
+      <c r="AS14" s="70"/>
+      <c r="AT14" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="AU14" s="61"/>
-      <c r="AV14" s="61"/>
-      <c r="AW14" s="61"/>
-      <c r="AX14" s="61"/>
-      <c r="AY14" s="61"/>
-      <c r="AZ14" s="61"/>
-      <c r="BA14" s="61"/>
-      <c r="BB14" s="61"/>
-      <c r="BC14" s="61"/>
-      <c r="BD14" s="61"/>
-      <c r="BE14" s="61"/>
-      <c r="BF14" s="61"/>
-      <c r="BG14" s="61"/>
-      <c r="BH14" s="61"/>
-      <c r="BI14" s="62"/>
+      <c r="AU14" s="65"/>
+      <c r="AV14" s="65"/>
+      <c r="AW14" s="65"/>
+      <c r="AX14" s="65"/>
+      <c r="AY14" s="65"/>
+      <c r="AZ14" s="65"/>
+      <c r="BA14" s="65"/>
+      <c r="BB14" s="65"/>
+      <c r="BC14" s="65"/>
+      <c r="BD14" s="65"/>
+      <c r="BE14" s="65"/>
+      <c r="BF14" s="65"/>
+      <c r="BG14" s="65"/>
+      <c r="BH14" s="65"/>
+      <c r="BI14" s="66"/>
       <c r="BJ14" s="1"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
@@ -12350,35 +12423,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="AT14:BI14"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="BD2:BI2"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
-    <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A1:L2"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="M2:Q2"/>
@@ -12395,6 +12439,35 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:O7"/>
     <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="BD2:BI2"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="BD1:BI1"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="AT14:BI14"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
   </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="2">
@@ -12413,6 +12486,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -12544,12 +12623,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -12560,6 +12633,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6513845-CAAC-46F8-AE5A-841CD9036AF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11CFAB00-E59E-479F-AE56-68D6BEAC86FA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12577,15 +12659,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6513845-CAAC-46F8-AE5A-841CD9036AF9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A031C656-AB27-471D-AE93-28F498CA5BD8}">
   <ds:schemaRefs>
